--- a/survey_templates/036_game_day_meal_planning_survey--survey_templates.xlsx
+++ b/survey_templates/036_game_day_meal_planning_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -597,7 +597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_headcount</t>
+          <t>game_day_meal_planning_survey_headcount_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_headcount</t>
+          <t>game_day_meal_planning_survey_headcount_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_headcount</t>
+          <t>game_day_meal_planning_survey_headcount_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How many guests are attending?</t>
+          <t>Game Day Meal Planning Survey Headcount 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_date_time</t>
+          <t>game_day_meal_planning_survey_date_time_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_address</t>
+          <t>game_day_meal_planning_survey_address_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_date</t>
+          <t>game_day_meal_planning_survey_date_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Game Day Meal Planning Survey Date 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_time</t>
+          <t>game_day_meal_planning_survey_time_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Game Day Meal Planning Survey Time 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional notes</t>
+          <t>Game Day Meal Planning Survey Additional Notes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1340,7 +1340,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>game_day_meal_planning_survey_contribution_commitments_choices</t>
+          <t>game_day_meal_planning_survey_contribution_commitments_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
